--- a/Horarios/Trenes/Merlo-Lobos/DomingoLasHeras.xlsx
+++ b/Horarios/Trenes/Merlo-Lobos/DomingoLasHeras.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Horarios" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -579,41 +579,35 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.2368055555555555</v>
+        <v>0.2770833333333333</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.2423611111111111</v>
+        <v>0.2826388888888889</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.2458333333333333</v>
+        <v>0.2861111111111111</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2534722222222222</v>
+        <v>0.2895833333333334</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.25625</v>
+        <v>0.2923611111111111</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2604166666666667</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+        <v>0.2972222222222222</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.3048611111111111</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.3097222222222222</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.3138888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -624,35 +618,35 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.2770833333333333</v>
+        <v>0.3784722222222222</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.3840277777777778</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.2861111111111111</v>
+        <v>0.3875</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.2895833333333334</v>
+        <v>0.3909722222222222</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.2923611111111111</v>
+        <v>0.39375</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.2972222222222222</v>
+        <v>0.3986111111111111</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.3048611111111111</v>
+        <v>0.40625</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.3097222222222222</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.3138888888888889</v>
+        <v>0.4152777777777778</v>
       </c>
     </row>
     <row r="5">
@@ -663,35 +657,35 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.3236111111111111</v>
+        <v>0.4798611111111111</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3291666666666667</v>
+        <v>0.4854166666666667</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.3326388888888889</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.3361111111111111</v>
+        <v>0.4923611111111111</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.3388888888888889</v>
+        <v>0.4951388888888889</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.3465277777777778</v>
+        <v>0.5</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.3541666666666667</v>
+        <v>0.5076388888888889</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.3590277777777778</v>
+        <v>0.5125</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.3631944444444444</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -702,35 +696,35 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.3784722222222222</v>
+        <v>0.58125</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3840277777777778</v>
+        <v>0.5868055555555556</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.3875</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.3909722222222222</v>
+        <v>0.59375</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.39375</v>
+        <v>0.5965277777777778</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.3986111111111111</v>
+        <v>0.6013888888888889</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.40625</v>
+        <v>0.6090277777777777</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.4111111111111111</v>
+        <v>0.6138888888888889</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.4152777777777778</v>
+        <v>0.6180555555555556</v>
       </c>
     </row>
     <row r="7">
@@ -741,41 +735,35 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.4395833333333333</v>
+        <v>0.6826388888888889</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.4451388888888889</v>
+        <v>0.6881944444444444</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4486111111111111</v>
+        <v>0.6916666666666667</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.45625</v>
+        <v>0.6951388888888889</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.4590277777777778</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.4631944444444445</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
+        <v>0.7027777777777777</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.7152777777777778</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>0.7194444444444444</v>
       </c>
     </row>
     <row r="8">
@@ -786,35 +774,35 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.4798611111111111</v>
+        <v>0.7840277777777778</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.4854166666666667</v>
+        <v>0.7895833333333333</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.7930555555555555</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.4923611111111111</v>
+        <v>0.7965277777777777</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.4951388888888889</v>
+        <v>0.7993055555555556</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.8041666666666667</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.5076388888888889</v>
+        <v>0.8118055555555556</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5125</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.5166666666666667</v>
+        <v>0.8208333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -825,35 +813,35 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.5263888888888889</v>
+        <v>0.8854166666666666</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.5319444444444444</v>
+        <v>0.8909722222222223</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.5354166666666667</v>
+        <v>0.8944444444444445</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.5388888888888889</v>
+        <v>0.8979166666666667</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.9006944444444445</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.5493055555555556</v>
+        <v>0.9055555555555556</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.5569444444444445</v>
+        <v>0.9131944444444444</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.5618055555555556</v>
+        <v>0.9180555555555555</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.5659722222222222</v>
+        <v>0.9222222222222223</v>
       </c>
     </row>
     <row r="10">
@@ -862,38 +850,16 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>2819</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.58125</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0.5868055555555556</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>0.5902777777777778</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.59375</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0.5965277777777778</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0.6013888888888889</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0.6090277777777777</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>0.6138888888888889</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.6180555555555556</v>
-      </c>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+      <c r="H10" s="1" t="n"/>
+      <c r="I10" s="1" t="n"/>
+      <c r="J10" s="1" t="n"/>
+      <c r="K10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -901,44 +867,16 @@
           <t>Sentido</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>2821</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0.6423611111111112</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0.6479166666666667</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0.6513888888888889</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.6590277777777778</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0.6618055555555555</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.6659722222222222</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="J11" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+      <c r="H11" s="1" t="n"/>
+      <c r="I11" s="1" t="n"/>
+      <c r="J11" s="1" t="n"/>
+      <c r="K11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -946,38 +884,16 @@
           <t>Las Heras</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>0.6826388888888889</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0.6881944444444444</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>0.6916666666666667</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.6951388888888889</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0.6979166666666666</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.7027777777777777</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0.7104166666666667</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>0.7152777777777778</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>0.7194444444444444</v>
-      </c>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+      <c r="H12" s="1" t="n"/>
+      <c r="I12" s="1" t="n"/>
+      <c r="J12" s="1" t="n"/>
+      <c r="K12" s="1" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -985,75 +901,31 @@
           <t>Estaciones</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>0.7291666666666666</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0.7347222222222223</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0.7381944444444445</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.7416666666666667</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0.7444444444444445</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0.7520833333333333</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0.7597222222222222</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>0.7645833333333333</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0.76875</v>
-      </c>
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="1" t="n"/>
+      <c r="D13" s="1" t="n"/>
+      <c r="E13" s="1" t="n"/>
+      <c r="F13" s="1" t="n"/>
+      <c r="G13" s="1" t="n"/>
+      <c r="H13" s="1" t="n"/>
+      <c r="I13" s="1" t="n"/>
+      <c r="J13" s="1" t="n"/>
+      <c r="K13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>2827</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0.7840277777777778</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0.7895833333333333</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.7930555555555555</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.7965277777777777</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0.7993055555555556</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0.8041666666666667</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0.8118055555555556</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>0.8166666666666667</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0.8208333333333333</v>
-      </c>
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="1" t="n"/>
+      <c r="E14" s="1" t="n"/>
+      <c r="F14" s="1" t="n"/>
+      <c r="G14" s="1" t="n"/>
+      <c r="H14" s="1" t="n"/>
+      <c r="I14" s="1" t="n"/>
+      <c r="J14" s="1" t="n"/>
+      <c r="K14" s="1" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1061,81 +933,31 @@
           <t>Formaciones</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>0.8451388888888889</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>0.8506944444444444</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0.8541666666666666</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.8618055555555556</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0.8645833333333334</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0.86875</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="1" t="n"/>
+      <c r="E15" s="1" t="n"/>
+      <c r="F15" s="1" t="n"/>
+      <c r="G15" s="1" t="n"/>
+      <c r="H15" s="1" t="n"/>
+      <c r="I15" s="1" t="n"/>
+      <c r="J15" s="1" t="n"/>
+      <c r="K15" s="1" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>2831</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>0.8854166666666666</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>0.8909722222222223</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>0.8944444444444445</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.8979166666666667</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0.9006944444444445</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0.9055555555555556</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0.9131944444444444</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>0.9180555555555555</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0.9222222222222223</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="1" t="n"/>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="1" t="n"/>
+      <c r="G16" s="1" t="n"/>
+      <c r="H16" s="1" t="n"/>
+      <c r="I16" s="1" t="n"/>
+      <c r="J16" s="1" t="n"/>
+      <c r="K16" s="1" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1143,42 +965,20 @@
           <t>Vigencia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>0.9319444444444445</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0.9409722222222222</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0.9472222222222222</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>0.9548611111111112</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0.9625</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>0.9673611111111111</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>0.9715277777777778</v>
-      </c>
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="1" t="n"/>
+      <c r="D17" s="1" t="n"/>
+      <c r="E17" s="1" t="n"/>
+      <c r="F17" s="1" t="n"/>
+      <c r="G17" s="1" t="n"/>
+      <c r="H17" s="1" t="n"/>
+      <c r="I17" s="1" t="n"/>
+      <c r="J17" s="1" t="n"/>
+      <c r="K17" s="1" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46264</v>
+        <v>46299</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>

--- a/Horarios/Trenes/Merlo-Lobos/DomingoLasHeras.xlsx
+++ b/Horarios/Trenes/Merlo-Lobos/DomingoLasHeras.xlsx
@@ -579,35 +579,41 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.2770833333333333</v>
+        <v>0.2368055555555555</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.2826388888888889</v>
+        <v>0.2423611111111111</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.2861111111111111</v>
+        <v>0.2458333333333333</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.2895833333333334</v>
+        <v>0.2534722222222222</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.2923611111111111</v>
+        <v>0.25625</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2972222222222222</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0.3048611111111111</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.3097222222222222</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.3138888888888889</v>
+        <v>0.2604166666666667</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -618,35 +624,35 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.3784722222222222</v>
+        <v>0.2770833333333333</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.3840277777777778</v>
+        <v>0.2826388888888889</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.3875</v>
+        <v>0.2861111111111111</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.3909722222222222</v>
+        <v>0.2895833333333334</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.39375</v>
+        <v>0.2923611111111111</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.3986111111111111</v>
+        <v>0.2972222222222222</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.40625</v>
+        <v>0.3048611111111111</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.4111111111111111</v>
+        <v>0.3097222222222222</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.4152777777777778</v>
+        <v>0.3138888888888889</v>
       </c>
     </row>
     <row r="5">
@@ -657,35 +663,35 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.4798611111111111</v>
+        <v>0.3236111111111111</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.4854166666666667</v>
+        <v>0.3291666666666667</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.3326388888888889</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.4923611111111111</v>
+        <v>0.3361111111111111</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.4951388888888889</v>
+        <v>0.3388888888888889</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3465277777777778</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.5076388888888889</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5125</v>
+        <v>0.3590277777777778</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.5166666666666667</v>
+        <v>0.3631944444444444</v>
       </c>
     </row>
     <row r="6">
@@ -696,35 +702,35 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>2819</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.58125</v>
+        <v>0.3784722222222222</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.5868055555555556</v>
+        <v>0.3840277777777778</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.5902777777777778</v>
+        <v>0.3875</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.59375</v>
+        <v>0.3909722222222222</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5965277777777778</v>
+        <v>0.39375</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.6013888888888889</v>
+        <v>0.3986111111111111</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.6090277777777777</v>
+        <v>0.40625</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.6138888888888889</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.6180555555555556</v>
+        <v>0.4152777777777778</v>
       </c>
     </row>
     <row r="7">
@@ -735,35 +741,41 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.6826388888888889</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.6881944444444444</v>
+        <v>0.4451388888888889</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.6916666666666667</v>
+        <v>0.4486111111111111</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6951388888888889</v>
+        <v>0.45625</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.4590277777777778</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7027777777777777</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0.7104166666666667</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>0.7152777777777778</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.7194444444444444</v>
+        <v>0.4631944444444445</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J7" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -774,35 +786,35 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.7840277777777778</v>
+        <v>0.4798611111111111</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.7895833333333333</v>
+        <v>0.4854166666666667</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.7930555555555555</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.7965277777777777</v>
+        <v>0.4923611111111111</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.7993055555555556</v>
+        <v>0.4951388888888889</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8041666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.8118055555555556</v>
+        <v>0.5076388888888889</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.5125</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.8208333333333333</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -813,35 +825,35 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.8854166666666666</v>
+        <v>0.5263888888888889</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.8909722222222223</v>
+        <v>0.5319444444444444</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.8944444444444445</v>
+        <v>0.5354166666666667</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.8979166666666667</v>
+        <v>0.5388888888888889</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.9006944444444445</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.9055555555555556</v>
+        <v>0.5493055555555556</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.9131944444444444</v>
+        <v>0.5569444444444445</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9180555555555555</v>
+        <v>0.5618055555555556</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.9222222222222223</v>
+        <v>0.5659722222222222</v>
       </c>
     </row>
     <row r="10">
@@ -850,16 +862,38 @@
           <t>Domingo</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n"/>
-      <c r="C10" s="1" t="n"/>
-      <c r="D10" s="1" t="n"/>
-      <c r="E10" s="1" t="n"/>
-      <c r="F10" s="1" t="n"/>
-      <c r="G10" s="1" t="n"/>
-      <c r="H10" s="1" t="n"/>
-      <c r="I10" s="1" t="n"/>
-      <c r="J10" s="1" t="n"/>
-      <c r="K10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>2819</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>0.58125</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.5868055555555556</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.5902777777777778</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.5965277777777778</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.6013888888888889</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.6090277777777777</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.6138888888888889</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.6180555555555556</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -867,16 +901,44 @@
           <t>Sentido</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n"/>
-      <c r="C11" s="1" t="n"/>
-      <c r="D11" s="1" t="n"/>
-      <c r="E11" s="1" t="n"/>
-      <c r="F11" s="1" t="n"/>
-      <c r="G11" s="1" t="n"/>
-      <c r="H11" s="1" t="n"/>
-      <c r="I11" s="1" t="n"/>
-      <c r="J11" s="1" t="n"/>
-      <c r="K11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>2821</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>0.6423611111111112</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.6513888888888889</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.6590277777777778</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.6618055555555555</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.6659722222222222</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J11" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -884,16 +946,38 @@
           <t>Las Heras</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n"/>
-      <c r="C12" s="1" t="n"/>
-      <c r="D12" s="1" t="n"/>
-      <c r="E12" s="1" t="n"/>
-      <c r="F12" s="1" t="n"/>
-      <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
-      <c r="I12" s="1" t="n"/>
-      <c r="J12" s="1" t="n"/>
-      <c r="K12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>0.6826388888888889</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.6881944444444444</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.6916666666666667</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.6951388888888889</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.6979166666666666</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.7027777777777777</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.7104166666666667</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.7152777777777778</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.7194444444444444</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -901,31 +985,75 @@
           <t>Estaciones</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
-      <c r="E13" s="1" t="n"/>
-      <c r="F13" s="1" t="n"/>
-      <c r="G13" s="1" t="n"/>
-      <c r="H13" s="1" t="n"/>
-      <c r="I13" s="1" t="n"/>
-      <c r="J13" s="1" t="n"/>
-      <c r="K13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.7347222222222223</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.7381944444444445</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.7520833333333333</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0.7597222222222222</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.7645833333333333</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.76875</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="1" t="n"/>
-      <c r="C14" s="1" t="n"/>
-      <c r="D14" s="1" t="n"/>
-      <c r="E14" s="1" t="n"/>
-      <c r="F14" s="1" t="n"/>
-      <c r="G14" s="1" t="n"/>
-      <c r="H14" s="1" t="n"/>
-      <c r="I14" s="1" t="n"/>
-      <c r="J14" s="1" t="n"/>
-      <c r="K14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>2827</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>0.7840277777777778</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.7895833333333333</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.7930555555555555</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.7965277777777777</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.7993055555555556</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.8041666666666667</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0.8118055555555556</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.8166666666666667</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.8208333333333333</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -933,31 +1061,81 @@
           <t>Formaciones</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="1" t="n"/>
-      <c r="E15" s="1" t="n"/>
-      <c r="F15" s="1" t="n"/>
-      <c r="G15" s="1" t="n"/>
-      <c r="H15" s="1" t="n"/>
-      <c r="I15" s="1" t="n"/>
-      <c r="J15" s="1" t="n"/>
-      <c r="K15" s="1" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>0.8451388888888889</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.8506944444444444</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.8541666666666666</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.8618055555555556</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0.8645833333333334</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.86875</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="J15" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B16" s="1" t="n"/>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
-      <c r="G16" s="1" t="n"/>
-      <c r="H16" s="1" t="n"/>
-      <c r="I16" s="1" t="n"/>
-      <c r="J16" s="1" t="n"/>
-      <c r="K16" s="1" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>2831</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>0.8854166666666666</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.8909722222222223</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.8944444444444445</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.8979166666666667</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0.9006944444444445</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0.9055555555555556</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0.9131944444444444</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.9180555555555555</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.9222222222222223</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -965,20 +1143,42 @@
           <t>Vigencia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n"/>
-      <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
-      <c r="E17" s="1" t="n"/>
-      <c r="F17" s="1" t="n"/>
-      <c r="G17" s="1" t="n"/>
-      <c r="H17" s="1" t="n"/>
-      <c r="I17" s="1" t="n"/>
-      <c r="J17" s="1" t="n"/>
-      <c r="K17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>0.9319444444444445</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.9409722222222222</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0.9472222222222222</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.9548611111111112</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.9673611111111111</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.9715277777777778</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46299</v>
+        <v>46313</v>
       </c>
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="1" t="n"/>
